--- a/templates/plantilla_form1.xlsx
+++ b/templates/plantilla_form1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brs77\Desktop\Juanes\Monitoria\extension-server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DAB98A-8AA4-43C2-AC7A-0DD88E2D068B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A165302F-6B9A-43F5-988B-E0F055F8A11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1127,124 +1127,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1252,13 +1149,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -1289,6 +1196,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1312,6 +1222,105 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1320,15 +1329,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1575,8 +1575,8 @@
       <xdr:rowOff>32846</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>298174</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>325716</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>1418</xdr:rowOff>
     </xdr:to>
@@ -1926,14 +1926,14 @@
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
     <col min="2" max="2" width="6.88671875" customWidth="1"/>
-    <col min="3" max="3" width="3" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="5.88671875" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" customWidth="1"/>
-    <col min="8" max="8" width="3.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" customWidth="1"/>
     <col min="11" max="11" width="6.6640625" customWidth="1"/>
     <col min="12" max="12" width="1" customWidth="1"/>
     <col min="13" max="13" width="1.44140625" customWidth="1"/>
@@ -1999,36 +1999,36 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="76" t="s">
+      <c r="O3" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
     </row>
     <row r="4" spans="1:18" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="78" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="118" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="56"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="74"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="O4" s="79" t="s">
+      <c r="O4" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="P4" s="56"/>
+      <c r="P4" s="74"/>
       <c r="Q4" s="5" t="s">
         <v>3</v>
       </c>
@@ -2038,27 +2038,27 @@
     </row>
     <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="64"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="81" t="s">
+      <c r="O5" s="122" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="82" t="s">
+      <c r="P5" s="62"/>
+      <c r="Q5" s="123" t="s">
         <v>101</v>
       </c>
-      <c r="R5" s="82" t="s">
+      <c r="R5" s="123" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2077,55 +2077,55 @@
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="83"/>
-      <c r="R6" s="83"/>
+      <c r="O6" s="66"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="124"/>
+      <c r="R6" s="124"/>
     </row>
     <row r="7" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="55"/>
+      <c r="B7" s="73"/>
       <c r="C7" s="46"/>
       <c r="D7" s="7" t="s">
         <v>105</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="80" t="s">
+      <c r="F7" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
       <c r="I7" s="7" t="s">
         <v>106</v>
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="80" t="s">
+      <c r="L7" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="55"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="73"/>
       <c r="Q7" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="72"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
+      <c r="J8" s="120"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -2134,412 +2134,412 @@
       <c r="R8" s="6"/>
     </row>
     <row r="9" spans="1:18" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="73" t="s">
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="61"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="62"/>
     </row>
     <row r="10" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="75" t="s">
+      <c r="A10" s="98" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="75" t="s">
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="56"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="74"/>
     </row>
     <row r="11" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="61"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="58"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="58"/>
+      <c r="Q11" s="58"/>
+      <c r="R11" s="62"/>
     </row>
     <row r="12" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="56"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="74"/>
       <c r="E12" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F12" s="74" t="s">
+      <c r="F12" s="125" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="74"/>
       <c r="K12" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="L12" s="74" t="s">
+      <c r="L12" s="125" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="56"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="73"/>
+      <c r="Q12" s="74"/>
       <c r="R12" s="10" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="125" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="74"/>
       <c r="E13" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F13" s="74" t="s">
+      <c r="F13" s="125" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="56"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="74"/>
       <c r="K13" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="L13" s="74" t="s">
+      <c r="L13" s="125" t="s">
         <v>16</v>
       </c>
-      <c r="M13" s="55"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="56"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="74"/>
       <c r="R13" s="10" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="74" t="s">
+      <c r="A14" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="56"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="74"/>
       <c r="E14" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F14" s="74" t="s">
+      <c r="F14" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="56"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="74"/>
       <c r="K14" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="L14" s="74" t="s">
+      <c r="L14" s="125" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="55"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="56"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="73"/>
+      <c r="Q14" s="74"/>
       <c r="R14" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="55"/>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="56"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="73"/>
+      <c r="R15" s="74"/>
     </row>
     <row r="16" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="56"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="73"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="73"/>
+      <c r="R16" s="74"/>
     </row>
     <row r="17" spans="1:18" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="56"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="73"/>
+      <c r="R17" s="74"/>
     </row>
     <row r="18" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="58" t="s">
+      <c r="A18" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="56"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="73"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="73"/>
+      <c r="R18" s="74"/>
     </row>
     <row r="19" spans="1:18" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="55"/>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="56"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="73"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="73"/>
+      <c r="O19" s="73"/>
+      <c r="P19" s="73"/>
+      <c r="Q19" s="73"/>
+      <c r="R19" s="74"/>
     </row>
     <row r="20" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="87" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="55"/>
-      <c r="P20" s="55"/>
-      <c r="Q20" s="55"/>
-      <c r="R20" s="56"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="73"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="73"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="73"/>
+      <c r="R20" s="74"/>
     </row>
     <row r="21" spans="1:18" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="56"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="73"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="73"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="73"/>
+      <c r="Q21" s="73"/>
+      <c r="R21" s="74"/>
     </row>
     <row r="22" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="55"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="56"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="73"/>
+      <c r="Q22" s="73"/>
+      <c r="R22" s="74"/>
     </row>
     <row r="23" spans="1:18" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="56"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="73"/>
+      <c r="P23" s="73"/>
+      <c r="Q23" s="73"/>
+      <c r="R23" s="74"/>
     </row>
     <row r="24" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="55"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="56"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="73"/>
+      <c r="O24" s="73"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="73"/>
+      <c r="R24" s="74"/>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="55"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="56"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="73"/>
+      <c r="O25" s="73"/>
+      <c r="P25" s="73"/>
+      <c r="Q25" s="73"/>
+      <c r="R25" s="74"/>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
@@ -2548,24 +2548,24 @@
       <c r="B26" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C26" s="100" t="s">
+      <c r="C26" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="60"/>
+      <c r="D26" s="58"/>
       <c r="E26" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="F26" s="69" t="s">
+      <c r="F26" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="60"/>
+      <c r="G26" s="58"/>
       <c r="H26" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="I26" s="69" t="s">
+      <c r="I26" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="J26" s="60"/>
+      <c r="J26" s="58"/>
       <c r="K26" s="12" t="s">
         <v>138</v>
       </c>
@@ -2573,10 +2573,10 @@
       <c r="M26" s="14"/>
       <c r="N26" s="14"/>
       <c r="O26" s="14"/>
-      <c r="P26" s="70" t="s">
+      <c r="P26" s="131" t="s">
         <v>30</v>
       </c>
-      <c r="Q26" s="60"/>
+      <c r="Q26" s="58"/>
       <c r="R26" s="15" t="s">
         <v>139</v>
       </c>
@@ -2585,10 +2585,10 @@
       <c r="A27" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B27" s="111" t="s">
+      <c r="B27" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="72"/>
+      <c r="C27" s="64"/>
       <c r="D27" s="47"/>
       <c r="E27" s="47"/>
       <c r="F27" s="47"/>
@@ -2628,26 +2628,26 @@
       <c r="R28" s="40"/>
     </row>
     <row r="29" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="112" t="s">
+      <c r="A29" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="113"/>
-      <c r="C29" s="113"/>
-      <c r="D29" s="113"/>
-      <c r="E29" s="113"/>
-      <c r="F29" s="113"/>
-      <c r="G29" s="113"/>
-      <c r="H29" s="113"/>
-      <c r="I29" s="113"/>
-      <c r="J29" s="113"/>
-      <c r="K29" s="113"/>
-      <c r="L29" s="113"/>
-      <c r="M29" s="113"/>
-      <c r="N29" s="113"/>
-      <c r="O29" s="113"/>
-      <c r="P29" s="113"/>
-      <c r="Q29" s="113"/>
-      <c r="R29" s="114"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="80"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="80"/>
+      <c r="R29" s="81"/>
     </row>
     <row r="30" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
@@ -2657,147 +2657,147 @@
         <v>142</v>
       </c>
       <c r="C30" s="43"/>
-      <c r="D30" s="115" t="s">
+      <c r="D30" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="116"/>
-      <c r="F30" s="116"/>
-      <c r="G30" s="116"/>
-      <c r="H30" s="132" t="s">
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="54" t="s">
         <v>143</v>
       </c>
       <c r="I30" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="J30" s="132" t="s">
+      <c r="J30" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="K30" s="117" t="s">
+      <c r="K30" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="L30" s="116"/>
-      <c r="M30" s="116"/>
+      <c r="L30" s="83"/>
+      <c r="M30" s="83"/>
       <c r="N30" s="45" t="s">
         <v>145</v>
       </c>
       <c r="O30" s="42"/>
-      <c r="P30" s="118" t="s">
+      <c r="P30" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="Q30" s="116"/>
-      <c r="R30" s="133" t="s">
+      <c r="Q30" s="83"/>
+      <c r="R30" s="55" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="119" t="s">
+      <c r="A31" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="63"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="63"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="63"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="63"/>
-      <c r="R31" s="64"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="68"/>
     </row>
     <row r="32" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="57" t="s">
+      <c r="A32" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55"/>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="55"/>
-      <c r="M32" s="55"/>
-      <c r="N32" s="55"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="55"/>
-      <c r="Q32" s="55"/>
-      <c r="R32" s="56"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="73"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="73"/>
+      <c r="R32" s="74"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55"/>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="55"/>
-      <c r="N33" s="55"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="56"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="73"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="73"/>
+      <c r="O33" s="73"/>
+      <c r="P33" s="73"/>
+      <c r="Q33" s="73"/>
+      <c r="R33" s="74"/>
     </row>
     <row r="34" spans="1:18" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="120" t="s">
+      <c r="A34" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="60"/>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="60"/>
-      <c r="K34" s="60"/>
-      <c r="L34" s="60"/>
-      <c r="M34" s="60"/>
-      <c r="N34" s="60"/>
-      <c r="O34" s="60"/>
-      <c r="P34" s="60"/>
-      <c r="Q34" s="60"/>
-      <c r="R34" s="61"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="58"/>
+      <c r="P34" s="58"/>
+      <c r="Q34" s="58"/>
+      <c r="R34" s="62"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="55"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="55"/>
-      <c r="J35" s="55"/>
-      <c r="K35" s="55"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="55"/>
-      <c r="N35" s="55"/>
-      <c r="O35" s="55"/>
-      <c r="P35" s="55"/>
-      <c r="Q35" s="55"/>
-      <c r="R35" s="56"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73"/>
+      <c r="J35" s="73"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="73"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="73"/>
+      <c r="O35" s="73"/>
+      <c r="P35" s="73"/>
+      <c r="Q35" s="73"/>
+      <c r="R35" s="74"/>
     </row>
     <row r="36" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
@@ -2806,30 +2806,30 @@
       <c r="B36" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="60"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
       <c r="G36" s="50" t="s">
         <v>147</v>
       </c>
       <c r="H36" s="51"/>
-      <c r="I36" s="68" t="s">
+      <c r="I36" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="J36" s="60"/>
+      <c r="J36" s="58"/>
       <c r="K36" s="52" t="s">
         <v>123</v>
       </c>
       <c r="L36" s="19"/>
       <c r="M36" s="19"/>
-      <c r="N36" s="68" t="s">
+      <c r="N36" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="O36" s="60"/>
-      <c r="P36" s="60"/>
+      <c r="O36" s="58"/>
+      <c r="P36" s="58"/>
       <c r="Q36" s="51" t="s">
         <v>124</v>
       </c>
@@ -2876,638 +2876,638 @@
       <c r="R38" s="27"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="54" t="s">
+      <c r="B39" s="73"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="55"/>
-      <c r="P39" s="55"/>
-      <c r="Q39" s="55"/>
-      <c r="R39" s="56"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="73"/>
+      <c r="L39" s="73"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="73"/>
+      <c r="O39" s="73"/>
+      <c r="P39" s="73"/>
+      <c r="Q39" s="73"/>
+      <c r="R39" s="74"/>
     </row>
     <row r="40" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="127" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="60"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="59" t="s">
+      <c r="B40" s="58"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="127" t="s">
         <v>118</v>
       </c>
-      <c r="E40" s="60"/>
-      <c r="F40" s="60"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="65" t="s">
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="97" t="s">
         <v>119</v>
       </c>
-      <c r="I40" s="66"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
-      <c r="N40" s="66"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="65" t="s">
+      <c r="I40" s="128"/>
+      <c r="J40" s="128"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="128"/>
+      <c r="N40" s="128"/>
+      <c r="O40" s="129"/>
+      <c r="P40" s="97" t="s">
         <v>120</v>
       </c>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="67"/>
+      <c r="Q40" s="128"/>
+      <c r="R40" s="129"/>
     </row>
     <row r="41" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="62"/>
-      <c r="B41" s="63"/>
-      <c r="C41" s="64"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="65" t="s">
+      <c r="A41" s="66"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
-      <c r="N41" s="66"/>
-      <c r="O41" s="66"/>
-      <c r="P41" s="66"/>
-      <c r="Q41" s="66"/>
-      <c r="R41" s="67"/>
+      <c r="I41" s="128"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="128"/>
+      <c r="L41" s="128"/>
+      <c r="M41" s="128"/>
+      <c r="N41" s="128"/>
+      <c r="O41" s="128"/>
+      <c r="P41" s="128"/>
+      <c r="Q41" s="128"/>
+      <c r="R41" s="129"/>
     </row>
     <row r="42" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="108" t="s">
+      <c r="A42" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="109"/>
-      <c r="C42" s="109"/>
-      <c r="D42" s="109"/>
-      <c r="E42" s="109"/>
-      <c r="F42" s="109"/>
-      <c r="G42" s="109"/>
-      <c r="H42" s="109"/>
-      <c r="I42" s="109"/>
-      <c r="J42" s="109"/>
-      <c r="K42" s="109"/>
-      <c r="L42" s="109"/>
-      <c r="M42" s="109"/>
-      <c r="N42" s="109"/>
-      <c r="O42" s="109"/>
-      <c r="P42" s="109"/>
-      <c r="Q42" s="109"/>
-      <c r="R42" s="110"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
+      <c r="I42" s="76"/>
+      <c r="J42" s="76"/>
+      <c r="K42" s="76"/>
+      <c r="L42" s="76"/>
+      <c r="M42" s="76"/>
+      <c r="N42" s="76"/>
+      <c r="O42" s="76"/>
+      <c r="P42" s="76"/>
+      <c r="Q42" s="76"/>
+      <c r="R42" s="77"/>
     </row>
     <row r="43" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="102" t="s">
+      <c r="A43" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="B43" s="60"/>
-      <c r="C43" s="60"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="60"/>
-      <c r="F43" s="60"/>
-      <c r="G43" s="60"/>
-      <c r="H43" s="60"/>
-      <c r="I43" s="60"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="60"/>
-      <c r="L43" s="60"/>
-      <c r="M43" s="60"/>
-      <c r="N43" s="60"/>
-      <c r="O43" s="60"/>
-      <c r="P43" s="60"/>
-      <c r="Q43" s="60"/>
-      <c r="R43" s="61"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="58"/>
+      <c r="K43" s="58"/>
+      <c r="L43" s="58"/>
+      <c r="M43" s="58"/>
+      <c r="N43" s="58"/>
+      <c r="O43" s="58"/>
+      <c r="P43" s="58"/>
+      <c r="Q43" s="58"/>
+      <c r="R43" s="62"/>
     </row>
     <row r="44" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="103"/>
-      <c r="B44" s="72"/>
-      <c r="C44" s="72"/>
-      <c r="D44" s="72"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="72"/>
-      <c r="H44" s="72"/>
-      <c r="I44" s="72"/>
-      <c r="J44" s="72"/>
-      <c r="K44" s="72"/>
-      <c r="L44" s="72"/>
-      <c r="M44" s="72"/>
-      <c r="N44" s="72"/>
-      <c r="O44" s="72"/>
-      <c r="P44" s="72"/>
-      <c r="Q44" s="72"/>
-      <c r="R44" s="104"/>
+      <c r="A44" s="63"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="64"/>
+      <c r="J44" s="64"/>
+      <c r="K44" s="64"/>
+      <c r="L44" s="64"/>
+      <c r="M44" s="64"/>
+      <c r="N44" s="64"/>
+      <c r="O44" s="64"/>
+      <c r="P44" s="64"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="65"/>
     </row>
     <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="62"/>
-      <c r="B45" s="63"/>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
-      <c r="F45" s="63"/>
-      <c r="G45" s="63"/>
-      <c r="H45" s="63"/>
-      <c r="I45" s="63"/>
-      <c r="J45" s="63"/>
-      <c r="K45" s="63"/>
-      <c r="L45" s="63"/>
-      <c r="M45" s="63"/>
-      <c r="N45" s="63"/>
-      <c r="O45" s="63"/>
-      <c r="P45" s="63"/>
-      <c r="Q45" s="63"/>
-      <c r="R45" s="64"/>
+      <c r="A45" s="66"/>
+      <c r="B45" s="67"/>
+      <c r="C45" s="67"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="67"/>
+      <c r="I45" s="67"/>
+      <c r="J45" s="67"/>
+      <c r="K45" s="67"/>
+      <c r="L45" s="67"/>
+      <c r="M45" s="67"/>
+      <c r="N45" s="67"/>
+      <c r="O45" s="67"/>
+      <c r="P45" s="67"/>
+      <c r="Q45" s="67"/>
+      <c r="R45" s="68"/>
     </row>
     <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="105" t="s">
+      <c r="A46" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="106"/>
-      <c r="C46" s="106"/>
-      <c r="D46" s="106"/>
-      <c r="E46" s="106"/>
-      <c r="F46" s="106"/>
-      <c r="G46" s="106"/>
-      <c r="H46" s="106"/>
-      <c r="I46" s="106"/>
-      <c r="J46" s="106"/>
-      <c r="K46" s="106"/>
-      <c r="L46" s="106"/>
-      <c r="M46" s="106"/>
-      <c r="N46" s="106"/>
-      <c r="O46" s="106"/>
-      <c r="P46" s="106"/>
-      <c r="Q46" s="106"/>
-      <c r="R46" s="107"/>
+      <c r="B46" s="70"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="70"/>
+      <c r="M46" s="70"/>
+      <c r="N46" s="70"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="70"/>
+      <c r="Q46" s="70"/>
+      <c r="R46" s="71"/>
     </row>
     <row r="47" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="102" t="s">
+      <c r="A47" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="B47" s="60"/>
-      <c r="C47" s="60"/>
-      <c r="D47" s="60"/>
-      <c r="E47" s="60"/>
-      <c r="F47" s="60"/>
-      <c r="G47" s="60"/>
-      <c r="H47" s="60"/>
-      <c r="I47" s="60"/>
-      <c r="J47" s="60"/>
-      <c r="K47" s="60"/>
-      <c r="L47" s="60"/>
-      <c r="M47" s="60"/>
-      <c r="N47" s="60"/>
-      <c r="O47" s="60"/>
-      <c r="P47" s="60"/>
-      <c r="Q47" s="60"/>
-      <c r="R47" s="61"/>
+      <c r="B47" s="58"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="58"/>
+      <c r="K47" s="58"/>
+      <c r="L47" s="58"/>
+      <c r="M47" s="58"/>
+      <c r="N47" s="58"/>
+      <c r="O47" s="58"/>
+      <c r="P47" s="58"/>
+      <c r="Q47" s="58"/>
+      <c r="R47" s="62"/>
     </row>
     <row r="48" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="62"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="63"/>
-      <c r="D48" s="63"/>
-      <c r="E48" s="63"/>
-      <c r="F48" s="63"/>
-      <c r="G48" s="63"/>
-      <c r="H48" s="63"/>
-      <c r="I48" s="63"/>
-      <c r="J48" s="63"/>
-      <c r="K48" s="63"/>
-      <c r="L48" s="63"/>
-      <c r="M48" s="63"/>
-      <c r="N48" s="63"/>
-      <c r="O48" s="63"/>
-      <c r="P48" s="63"/>
-      <c r="Q48" s="63"/>
-      <c r="R48" s="64"/>
+      <c r="A48" s="66"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="67"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="67"/>
+      <c r="K48" s="67"/>
+      <c r="L48" s="67"/>
+      <c r="M48" s="67"/>
+      <c r="N48" s="67"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="67"/>
+      <c r="Q48" s="67"/>
+      <c r="R48" s="68"/>
     </row>
     <row r="49" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="54" t="s">
+      <c r="A49" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="55"/>
-      <c r="C49" s="55"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="55"/>
-      <c r="H49" s="55"/>
-      <c r="I49" s="55"/>
-      <c r="J49" s="55"/>
-      <c r="K49" s="55"/>
-      <c r="L49" s="55"/>
-      <c r="M49" s="55"/>
-      <c r="N49" s="55"/>
-      <c r="O49" s="55"/>
-      <c r="P49" s="55"/>
-      <c r="Q49" s="55"/>
-      <c r="R49" s="56"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73"/>
+      <c r="J49" s="73"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="73"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="73"/>
+      <c r="O49" s="73"/>
+      <c r="P49" s="73"/>
+      <c r="Q49" s="73"/>
+      <c r="R49" s="74"/>
     </row>
     <row r="50" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="121" t="s">
+      <c r="A50" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="122"/>
+      <c r="B50" s="90"/>
       <c r="C50" s="36" t="s">
         <v>125</v>
       </c>
       <c r="D50" s="36"/>
-      <c r="E50" s="121" t="s">
+      <c r="E50" s="89" t="s">
         <v>53</v>
       </c>
-      <c r="F50" s="122"/>
-      <c r="G50" s="122"/>
-      <c r="H50" s="122"/>
+      <c r="F50" s="90"/>
+      <c r="G50" s="90"/>
+      <c r="H50" s="90"/>
       <c r="I50" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="J50" s="123" t="s">
+      <c r="J50" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="K50" s="124"/>
-      <c r="L50" s="124"/>
-      <c r="M50" s="124"/>
-      <c r="N50" s="124"/>
-      <c r="O50" s="124"/>
-      <c r="P50" s="124"/>
+      <c r="K50" s="92"/>
+      <c r="L50" s="92"/>
+      <c r="M50" s="92"/>
+      <c r="N50" s="92"/>
+      <c r="O50" s="92"/>
+      <c r="P50" s="92"/>
       <c r="Q50" s="36" t="s">
         <v>127</v>
       </c>
       <c r="R50" s="29"/>
     </row>
     <row r="51" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="54" t="s">
+      <c r="A51" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="55"/>
-      <c r="C51" s="55"/>
-      <c r="D51" s="55"/>
-      <c r="E51" s="55"/>
-      <c r="F51" s="55"/>
-      <c r="G51" s="55"/>
-      <c r="H51" s="55"/>
-      <c r="I51" s="56"/>
-      <c r="J51" s="125" t="s">
+      <c r="B51" s="73"/>
+      <c r="C51" s="73"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="74"/>
+      <c r="J51" s="93" t="s">
         <v>128</v>
       </c>
-      <c r="K51" s="55"/>
-      <c r="L51" s="55"/>
-      <c r="M51" s="55"/>
-      <c r="N51" s="55"/>
-      <c r="O51" s="55"/>
-      <c r="P51" s="55"/>
-      <c r="Q51" s="55"/>
-      <c r="R51" s="56"/>
+      <c r="K51" s="73"/>
+      <c r="L51" s="73"/>
+      <c r="M51" s="73"/>
+      <c r="N51" s="73"/>
+      <c r="O51" s="73"/>
+      <c r="P51" s="73"/>
+      <c r="Q51" s="73"/>
+      <c r="R51" s="74"/>
     </row>
     <row r="52" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="126" t="s">
+      <c r="A52" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="127"/>
-      <c r="C52" s="127"/>
-      <c r="D52" s="127"/>
-      <c r="E52" s="127"/>
-      <c r="F52" s="127"/>
-      <c r="G52" s="127"/>
-      <c r="H52" s="127"/>
-      <c r="I52" s="127"/>
-      <c r="J52" s="127"/>
-      <c r="K52" s="127"/>
-      <c r="L52" s="127"/>
-      <c r="M52" s="127"/>
-      <c r="N52" s="127"/>
-      <c r="O52" s="127"/>
-      <c r="P52" s="127"/>
-      <c r="Q52" s="127"/>
-      <c r="R52" s="128"/>
+      <c r="B52" s="95"/>
+      <c r="C52" s="95"/>
+      <c r="D52" s="95"/>
+      <c r="E52" s="95"/>
+      <c r="F52" s="95"/>
+      <c r="G52" s="95"/>
+      <c r="H52" s="95"/>
+      <c r="I52" s="95"/>
+      <c r="J52" s="95"/>
+      <c r="K52" s="95"/>
+      <c r="L52" s="95"/>
+      <c r="M52" s="95"/>
+      <c r="N52" s="95"/>
+      <c r="O52" s="95"/>
+      <c r="P52" s="95"/>
+      <c r="Q52" s="95"/>
+      <c r="R52" s="96"/>
     </row>
     <row r="53" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="65" t="s">
+      <c r="A53" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="55"/>
-      <c r="C53" s="55"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
-      <c r="F53" s="55"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="75" t="s">
+      <c r="B53" s="73"/>
+      <c r="C53" s="73"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="73"/>
+      <c r="G53" s="74"/>
+      <c r="H53" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="I53" s="55"/>
-      <c r="J53" s="55"/>
-      <c r="K53" s="55"/>
-      <c r="L53" s="55"/>
-      <c r="M53" s="55"/>
-      <c r="N53" s="55"/>
-      <c r="O53" s="55"/>
-      <c r="P53" s="55"/>
-      <c r="Q53" s="55"/>
-      <c r="R53" s="56"/>
+      <c r="I53" s="73"/>
+      <c r="J53" s="73"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="73"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="73"/>
+      <c r="O53" s="73"/>
+      <c r="P53" s="73"/>
+      <c r="Q53" s="73"/>
+      <c r="R53" s="74"/>
     </row>
     <row r="54" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="65" t="s">
+      <c r="A54" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="55"/>
-      <c r="C54" s="55"/>
-      <c r="D54" s="55"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="56"/>
-      <c r="H54" s="75" t="s">
+      <c r="B54" s="73"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="98" t="s">
         <v>93</v>
       </c>
-      <c r="I54" s="55"/>
-      <c r="J54" s="55"/>
-      <c r="K54" s="55"/>
-      <c r="L54" s="55"/>
-      <c r="M54" s="55"/>
-      <c r="N54" s="55"/>
-      <c r="O54" s="55"/>
-      <c r="P54" s="55"/>
-      <c r="Q54" s="55"/>
-      <c r="R54" s="56"/>
+      <c r="I54" s="73"/>
+      <c r="J54" s="73"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="73"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="73"/>
+      <c r="O54" s="73"/>
+      <c r="P54" s="73"/>
+      <c r="Q54" s="73"/>
+      <c r="R54" s="74"/>
     </row>
     <row r="55" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="65" t="s">
+      <c r="A55" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="55"/>
-      <c r="C55" s="55"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="55"/>
-      <c r="F55" s="55"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="75" t="s">
+      <c r="B55" s="73"/>
+      <c r="C55" s="73"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="73"/>
+      <c r="G55" s="74"/>
+      <c r="H55" s="98" t="s">
         <v>94</v>
       </c>
-      <c r="I55" s="55"/>
-      <c r="J55" s="55"/>
-      <c r="K55" s="55"/>
-      <c r="L55" s="55"/>
-      <c r="M55" s="55"/>
-      <c r="N55" s="55"/>
-      <c r="O55" s="55"/>
-      <c r="P55" s="55"/>
-      <c r="Q55" s="55"/>
-      <c r="R55" s="56"/>
+      <c r="I55" s="73"/>
+      <c r="J55" s="73"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="73"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="73"/>
+      <c r="O55" s="73"/>
+      <c r="P55" s="73"/>
+      <c r="Q55" s="73"/>
+      <c r="R55" s="74"/>
     </row>
     <row r="56" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="65" t="s">
+      <c r="A56" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="55"/>
-      <c r="C56" s="55"/>
-      <c r="D56" s="55"/>
-      <c r="E56" s="55"/>
-      <c r="F56" s="55"/>
-      <c r="G56" s="56"/>
-      <c r="H56" s="75" t="s">
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="73"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
+      <c r="G56" s="74"/>
+      <c r="H56" s="98" t="s">
         <v>95</v>
       </c>
-      <c r="I56" s="55"/>
-      <c r="J56" s="55"/>
-      <c r="K56" s="55"/>
-      <c r="L56" s="55"/>
-      <c r="M56" s="55"/>
-      <c r="N56" s="55"/>
-      <c r="O56" s="55"/>
-      <c r="P56" s="55"/>
-      <c r="Q56" s="55"/>
-      <c r="R56" s="56"/>
+      <c r="I56" s="73"/>
+      <c r="J56" s="73"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="73"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="73"/>
+      <c r="O56" s="73"/>
+      <c r="P56" s="73"/>
+      <c r="Q56" s="73"/>
+      <c r="R56" s="74"/>
     </row>
     <row r="57" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="55"/>
-      <c r="C57" s="55"/>
-      <c r="D57" s="55"/>
-      <c r="E57" s="55"/>
-      <c r="F57" s="55"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="75" t="s">
+      <c r="B57" s="73"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="74"/>
+      <c r="H57" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="I57" s="55"/>
-      <c r="J57" s="55"/>
-      <c r="K57" s="55"/>
-      <c r="L57" s="55"/>
-      <c r="M57" s="55"/>
-      <c r="N57" s="55"/>
-      <c r="O57" s="55"/>
-      <c r="P57" s="55"/>
-      <c r="Q57" s="55"/>
-      <c r="R57" s="56"/>
+      <c r="I57" s="73"/>
+      <c r="J57" s="73"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="73"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="73"/>
+      <c r="O57" s="73"/>
+      <c r="P57" s="73"/>
+      <c r="Q57" s="73"/>
+      <c r="R57" s="74"/>
     </row>
     <row r="58" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="65" t="s">
+      <c r="A58" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="55"/>
-      <c r="C58" s="55"/>
-      <c r="D58" s="55"/>
-      <c r="E58" s="55"/>
-      <c r="F58" s="55"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="75" t="s">
+      <c r="B58" s="73"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="73"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="74"/>
+      <c r="H58" s="98" t="s">
         <v>97</v>
       </c>
-      <c r="I58" s="55"/>
-      <c r="J58" s="55"/>
-      <c r="K58" s="55"/>
-      <c r="L58" s="55"/>
-      <c r="M58" s="55"/>
-      <c r="N58" s="55"/>
-      <c r="O58" s="55"/>
-      <c r="P58" s="55"/>
-      <c r="Q58" s="55"/>
-      <c r="R58" s="56"/>
+      <c r="I58" s="73"/>
+      <c r="J58" s="73"/>
+      <c r="K58" s="73"/>
+      <c r="L58" s="73"/>
+      <c r="M58" s="73"/>
+      <c r="N58" s="73"/>
+      <c r="O58" s="73"/>
+      <c r="P58" s="73"/>
+      <c r="Q58" s="73"/>
+      <c r="R58" s="74"/>
     </row>
     <row r="59" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="65" t="s">
+      <c r="A59" s="97" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="55"/>
-      <c r="C59" s="55"/>
-      <c r="D59" s="55"/>
-      <c r="E59" s="55"/>
-      <c r="F59" s="55"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="75" t="s">
+      <c r="B59" s="73"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="73"/>
+      <c r="E59" s="73"/>
+      <c r="F59" s="73"/>
+      <c r="G59" s="74"/>
+      <c r="H59" s="98" t="s">
         <v>98</v>
       </c>
-      <c r="I59" s="55"/>
-      <c r="J59" s="55"/>
-      <c r="K59" s="55"/>
-      <c r="L59" s="55"/>
-      <c r="M59" s="55"/>
-      <c r="N59" s="55"/>
-      <c r="O59" s="55"/>
-      <c r="P59" s="55"/>
-      <c r="Q59" s="55"/>
-      <c r="R59" s="56"/>
+      <c r="I59" s="73"/>
+      <c r="J59" s="73"/>
+      <c r="K59" s="73"/>
+      <c r="L59" s="73"/>
+      <c r="M59" s="73"/>
+      <c r="N59" s="73"/>
+      <c r="O59" s="73"/>
+      <c r="P59" s="73"/>
+      <c r="Q59" s="73"/>
+      <c r="R59" s="74"/>
     </row>
     <row r="60" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="73" t="s">
+      <c r="A60" s="99" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="60"/>
-      <c r="C60" s="60"/>
-      <c r="D60" s="60"/>
-      <c r="E60" s="60"/>
-      <c r="F60" s="60"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="87" t="s">
+      <c r="B60" s="58"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="62"/>
+      <c r="H60" s="110" t="s">
         <v>129</v>
       </c>
-      <c r="I60" s="60"/>
-      <c r="J60" s="60"/>
-      <c r="K60" s="60"/>
-      <c r="L60" s="60"/>
-      <c r="M60" s="60"/>
-      <c r="N60" s="60"/>
-      <c r="O60" s="60"/>
-      <c r="P60" s="60"/>
-      <c r="Q60" s="60"/>
-      <c r="R60" s="61"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="58"/>
+      <c r="K60" s="58"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
+      <c r="P60" s="58"/>
+      <c r="Q60" s="58"/>
+      <c r="R60" s="62"/>
     </row>
     <row r="61" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="54" t="s">
+      <c r="A61" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="55"/>
-      <c r="C61" s="55"/>
-      <c r="D61" s="55"/>
-      <c r="E61" s="55"/>
-      <c r="F61" s="55"/>
-      <c r="G61" s="55"/>
-      <c r="H61" s="55"/>
-      <c r="I61" s="55"/>
-      <c r="J61" s="55"/>
-      <c r="K61" s="55"/>
-      <c r="L61" s="55"/>
-      <c r="M61" s="55"/>
-      <c r="N61" s="55"/>
-      <c r="O61" s="55"/>
-      <c r="P61" s="55"/>
-      <c r="Q61" s="55"/>
-      <c r="R61" s="56"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
+      <c r="J61" s="73"/>
+      <c r="K61" s="73"/>
+      <c r="L61" s="73"/>
+      <c r="M61" s="73"/>
+      <c r="N61" s="73"/>
+      <c r="O61" s="73"/>
+      <c r="P61" s="73"/>
+      <c r="Q61" s="73"/>
+      <c r="R61" s="74"/>
     </row>
     <row r="62" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="96" t="s">
+      <c r="A62" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="B62" s="72"/>
+      <c r="B62" s="64"/>
       <c r="C62" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D62" s="94" t="s">
+      <c r="D62" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="E62" s="94"/>
-      <c r="F62" s="94"/>
-      <c r="G62" s="94"/>
-      <c r="I62" s="94" t="s">
+      <c r="E62" s="115"/>
+      <c r="F62" s="115"/>
+      <c r="G62" s="115"/>
+      <c r="I62" s="115" t="s">
         <v>31</v>
       </c>
       <c r="J62" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="K62" s="95" t="s">
+      <c r="K62" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="L62" s="98"/>
-      <c r="M62" s="88" t="s">
+      <c r="L62" s="105"/>
+      <c r="M62" s="111" t="s">
         <v>133</v>
       </c>
-      <c r="N62" s="63"/>
-      <c r="O62" s="63"/>
-      <c r="P62" s="63"/>
-      <c r="Q62" s="63"/>
-      <c r="R62" s="64"/>
+      <c r="N62" s="67"/>
+      <c r="O62" s="67"/>
+      <c r="P62" s="67"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="68"/>
     </row>
     <row r="63" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="72"/>
-      <c r="B63" s="72"/>
+      <c r="A63" s="64"/>
+      <c r="B63" s="64"/>
       <c r="C63" s="24"/>
-      <c r="D63" s="95"/>
-      <c r="E63" s="95"/>
-      <c r="F63" s="95"/>
-      <c r="G63" s="95"/>
-      <c r="H63" s="134" t="s">
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="104"/>
+      <c r="G63" s="104"/>
+      <c r="H63" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="I63" s="95"/>
+      <c r="I63" s="104"/>
       <c r="J63" s="30"/>
-      <c r="K63" s="99"/>
-      <c r="L63" s="99"/>
-      <c r="M63" s="89"/>
-      <c r="N63" s="60"/>
-      <c r="O63" s="60"/>
-      <c r="P63" s="60"/>
-      <c r="Q63" s="60"/>
-      <c r="R63" s="61"/>
+      <c r="K63" s="106"/>
+      <c r="L63" s="106"/>
+      <c r="M63" s="112"/>
+      <c r="N63" s="58"/>
+      <c r="O63" s="58"/>
+      <c r="P63" s="58"/>
+      <c r="Q63" s="58"/>
+      <c r="R63" s="62"/>
     </row>
     <row r="64" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="97" t="s">
+      <c r="A64" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="91"/>
-      <c r="C64" s="90" t="s">
+      <c r="B64" s="102"/>
+      <c r="C64" s="113" t="s">
         <v>134</v>
       </c>
-      <c r="D64" s="91"/>
-      <c r="E64" s="91"/>
-      <c r="F64" s="91"/>
-      <c r="G64" s="91"/>
-      <c r="H64" s="91"/>
-      <c r="I64" s="91"/>
-      <c r="J64" s="91"/>
-      <c r="K64" s="91"/>
-      <c r="L64" s="91"/>
-      <c r="M64" s="91"/>
-      <c r="N64" s="91"/>
-      <c r="O64" s="91"/>
-      <c r="P64" s="91"/>
-      <c r="Q64" s="91"/>
-      <c r="R64" s="92"/>
+      <c r="D64" s="102"/>
+      <c r="E64" s="102"/>
+      <c r="F64" s="102"/>
+      <c r="G64" s="102"/>
+      <c r="H64" s="102"/>
+      <c r="I64" s="102"/>
+      <c r="J64" s="102"/>
+      <c r="K64" s="102"/>
+      <c r="L64" s="102"/>
+      <c r="M64" s="102"/>
+      <c r="N64" s="102"/>
+      <c r="O64" s="102"/>
+      <c r="P64" s="102"/>
+      <c r="Q64" s="102"/>
+      <c r="R64" s="114"/>
     </row>
     <row r="65" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23"/>
-      <c r="B65" s="93"/>
-      <c r="C65" s="63"/>
-      <c r="D65" s="63"/>
-      <c r="E65" s="63"/>
-      <c r="F65" s="63"/>
-      <c r="G65" s="63"/>
-      <c r="H65" s="63"/>
+      <c r="B65" s="103"/>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
       <c r="I65" s="31"/>
-      <c r="J65" s="93"/>
-      <c r="K65" s="63"/>
-      <c r="L65" s="63"/>
-      <c r="M65" s="63"/>
-      <c r="N65" s="63"/>
-      <c r="O65" s="63"/>
-      <c r="P65" s="63"/>
-      <c r="Q65" s="63"/>
+      <c r="J65" s="103"/>
+      <c r="K65" s="67"/>
+      <c r="L65" s="67"/>
+      <c r="M65" s="67"/>
+      <c r="N65" s="67"/>
+      <c r="O65" s="67"/>
+      <c r="P65" s="67"/>
+      <c r="Q65" s="67"/>
       <c r="R65" s="31"/>
     </row>
     <row r="66" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3515,17 +3515,17 @@
       <c r="B66" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="C66" s="101"/>
-      <c r="D66" s="101"/>
-      <c r="E66" s="101"/>
-      <c r="F66" s="101"/>
-      <c r="G66" s="101"/>
-      <c r="H66" s="101"/>
+      <c r="C66" s="60"/>
+      <c r="D66" s="60"/>
+      <c r="E66" s="60"/>
+      <c r="F66" s="60"/>
+      <c r="G66" s="60"/>
+      <c r="H66" s="60"/>
       <c r="I66" s="31"/>
-      <c r="J66" s="84" t="s">
+      <c r="J66" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="K66" s="72"/>
+      <c r="K66" s="64"/>
       <c r="L66" s="32"/>
       <c r="M66" s="32"/>
       <c r="N66" s="32"/>
@@ -3536,71 +3536,71 @@
     </row>
     <row r="67" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
-      <c r="B67" s="84" t="s">
+      <c r="B67" s="107" t="s">
         <v>70</v>
       </c>
-      <c r="C67" s="72"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="72"/>
-      <c r="G67" s="72"/>
-      <c r="H67" s="72"/>
+      <c r="C67" s="64"/>
+      <c r="D67" s="64"/>
+      <c r="E67" s="64"/>
+      <c r="F67" s="64"/>
+      <c r="G67" s="64"/>
+      <c r="H67" s="64"/>
       <c r="I67" s="31"/>
-      <c r="J67" s="84" t="s">
+      <c r="J67" s="107" t="s">
         <v>71</v>
       </c>
-      <c r="K67" s="72"/>
-      <c r="L67" s="72"/>
-      <c r="M67" s="72"/>
-      <c r="N67" s="72"/>
-      <c r="O67" s="72"/>
-      <c r="P67" s="72"/>
-      <c r="Q67" s="72"/>
+      <c r="K67" s="64"/>
+      <c r="L67" s="64"/>
+      <c r="M67" s="64"/>
+      <c r="N67" s="64"/>
+      <c r="O67" s="64"/>
+      <c r="P67" s="64"/>
+      <c r="Q67" s="64"/>
       <c r="R67" s="31"/>
     </row>
     <row r="68" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="B68" s="55"/>
-      <c r="C68" s="55"/>
-      <c r="D68" s="55"/>
-      <c r="E68" s="55"/>
-      <c r="F68" s="55"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="55"/>
-      <c r="I68" s="55"/>
-      <c r="J68" s="55"/>
-      <c r="K68" s="55"/>
-      <c r="L68" s="55"/>
-      <c r="M68" s="55"/>
-      <c r="N68" s="55"/>
-      <c r="O68" s="55"/>
-      <c r="P68" s="55"/>
-      <c r="Q68" s="55"/>
-      <c r="R68" s="56"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="73"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="73"/>
+      <c r="H68" s="73"/>
+      <c r="I68" s="73"/>
+      <c r="J68" s="73"/>
+      <c r="K68" s="73"/>
+      <c r="L68" s="73"/>
+      <c r="M68" s="73"/>
+      <c r="N68" s="73"/>
+      <c r="O68" s="73"/>
+      <c r="P68" s="73"/>
+      <c r="Q68" s="73"/>
+      <c r="R68" s="74"/>
     </row>
     <row r="69" spans="1:18" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="86" t="s">
+      <c r="A69" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="63"/>
-      <c r="C69" s="63"/>
-      <c r="D69" s="63"/>
-      <c r="E69" s="63"/>
-      <c r="F69" s="63"/>
-      <c r="G69" s="63"/>
-      <c r="H69" s="63"/>
-      <c r="I69" s="63"/>
-      <c r="J69" s="63"/>
-      <c r="K69" s="63"/>
-      <c r="L69" s="63"/>
-      <c r="M69" s="63"/>
-      <c r="N69" s="63"/>
-      <c r="O69" s="63"/>
-      <c r="P69" s="63"/>
-      <c r="Q69" s="63"/>
-      <c r="R69" s="64"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="67"/>
+      <c r="K69" s="67"/>
+      <c r="L69" s="67"/>
+      <c r="M69" s="67"/>
+      <c r="N69" s="67"/>
+      <c r="O69" s="67"/>
+      <c r="P69" s="67"/>
+      <c r="Q69" s="67"/>
+      <c r="R69" s="68"/>
     </row>
     <row r="70" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
@@ -22284,6 +22284,89 @@
     </row>
   </sheetData>
   <mergeCells count="107">
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A16:R16"/>
+    <mergeCell ref="A17:R17"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="A19:R19"/>
+    <mergeCell ref="A20:R20"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:C41"/>
+    <mergeCell ref="D40:G41"/>
+    <mergeCell ref="H40:O40"/>
+    <mergeCell ref="P40:R40"/>
+    <mergeCell ref="H41:R41"/>
+    <mergeCell ref="A35:R35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="H39:R39"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="A21:R21"/>
+    <mergeCell ref="A22:R22"/>
+    <mergeCell ref="A23:R23"/>
+    <mergeCell ref="A24:R24"/>
+    <mergeCell ref="A25:R25"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="J10:R10"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:L4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="L7:P7"/>
+    <mergeCell ref="O5:P6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="A68:R68"/>
+    <mergeCell ref="A69:R69"/>
+    <mergeCell ref="H59:R59"/>
+    <mergeCell ref="H60:R60"/>
+    <mergeCell ref="A61:R61"/>
+    <mergeCell ref="M62:R62"/>
+    <mergeCell ref="M63:R63"/>
+    <mergeCell ref="C64:R64"/>
+    <mergeCell ref="J65:Q65"/>
+    <mergeCell ref="D62:G63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="J67:Q67"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="H53:R53"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="H54:R54"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A62:B63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="H55:R55"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="H56:R56"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="H57:R57"/>
+    <mergeCell ref="H58:R58"/>
+    <mergeCell ref="K62:L63"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="C66:H66"/>
@@ -22308,89 +22391,6 @@
     <mergeCell ref="J51:R51"/>
     <mergeCell ref="A52:R52"/>
     <mergeCell ref="A53:G53"/>
-    <mergeCell ref="H53:R53"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="H54:R54"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A62:B63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="B65:H65"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="H55:R55"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="H56:R56"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="H57:R57"/>
-    <mergeCell ref="H58:R58"/>
-    <mergeCell ref="K62:L63"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="A68:R68"/>
-    <mergeCell ref="A69:R69"/>
-    <mergeCell ref="H59:R59"/>
-    <mergeCell ref="H60:R60"/>
-    <mergeCell ref="A61:R61"/>
-    <mergeCell ref="M62:R62"/>
-    <mergeCell ref="M63:R63"/>
-    <mergeCell ref="C64:R64"/>
-    <mergeCell ref="J65:Q65"/>
-    <mergeCell ref="D62:G63"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="J67:Q67"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:L4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="L7:P7"/>
-    <mergeCell ref="O5:P6"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="J10:R10"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A16:R16"/>
-    <mergeCell ref="A17:R17"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="A19:R19"/>
-    <mergeCell ref="A20:R20"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:C41"/>
-    <mergeCell ref="D40:G41"/>
-    <mergeCell ref="H40:O40"/>
-    <mergeCell ref="P40:R40"/>
-    <mergeCell ref="H41:R41"/>
-    <mergeCell ref="A35:R35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="H39:R39"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="A21:R21"/>
-    <mergeCell ref="A22:R22"/>
-    <mergeCell ref="A23:R23"/>
-    <mergeCell ref="A24:R24"/>
-    <mergeCell ref="A25:R25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0.39370078740157483"/>
@@ -22533,10 +22533,10 @@
       <c r="Z4" s="33"/>
     </row>
     <row r="5" spans="1:26" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="132" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="72"/>
+      <c r="B5" s="64"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
       <c r="E5" s="33"/>
@@ -22711,10 +22711,10 @@
       <c r="Z10" s="33"/>
     </row>
     <row r="11" spans="1:26" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="130" t="s">
+      <c r="A11" s="133" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="131"/>
+      <c r="B11" s="134"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
       <c r="E11" s="33"/>
